--- a/artfynd/A 30281-2019 artfynd.xlsx
+++ b/artfynd/A 30281-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30281-2019 artfynd.xlsx
+++ b/artfynd/A 30281-2019 artfynd.xlsx
@@ -1681,7 +1681,7 @@
         <v>98838416</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>402727.7123937453</v>
+        <v>402728</v>
       </c>
       <c r="R10" t="n">
-        <v>6757828.288082589</v>
+        <v>6757828</v>
       </c>
       <c r="S10" t="n">
         <v>75</v>
@@ -1759,19 +1759,9 @@
           <t>2022-02-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-02-25</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 30281-2019 artfynd.xlsx
+++ b/artfynd/A 30281-2019 artfynd.xlsx
@@ -1681,7 +1681,7 @@
         <v>98838416</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
